--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,12 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604118.0581587028</v>
+        <v>604118</v>
       </c>
       <c r="R4" t="n">
-        <v>6792179.924868371</v>
+        <v>6792180</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -985,19 +980,9 @@
           <t>1986-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1986-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,12 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101665</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604118.0581587028</v>
+        <v>604118</v>
       </c>
       <c r="R5" t="n">
-        <v>6792179.924868371</v>
+        <v>6792180</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1111,19 +1091,9 @@
           <t>1986-07-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1986-07-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,12 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604118.0581587028</v>
+        <v>604118</v>
       </c>
       <c r="R6" t="n">
-        <v>6792179.924868371</v>
+        <v>6792180</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1237,19 +1202,9 @@
           <t>1986-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1986-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,12 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604118.0581587028</v>
+        <v>604118</v>
       </c>
       <c r="R7" t="n">
-        <v>6792179.924868371</v>
+        <v>6792180</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1363,19 +1313,9 @@
           <t>1986-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1986-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,12 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604118.0581587028</v>
+        <v>604118</v>
       </c>
       <c r="R8" t="n">
-        <v>6792179.924868371</v>
+        <v>6792180</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1489,19 +1424,9 @@
           <t>1986-07-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1986-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110682</v>
+        <v>110691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110691</v>
+        <v>110704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110774</v>
+        <v>110779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 15765-2025 artfynd.xlsx
+++ b/artfynd/A 15765-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>84486501</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>84486498</v>
       </c>
       <c r="B5" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>84486511</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>84486467</v>
       </c>
       <c r="B7" t="n">
-        <v>110779</v>
+        <v>110787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>84486510</v>
       </c>
       <c r="B8" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
